--- a/Team-Data/2008-09/2-12-2008-09.xlsx
+++ b/Team-Data/2008-09/2-12-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -745,10 +812,10 @@
         <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>28</v>
@@ -757,7 +824,7 @@
         <v>23</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
         <v>13</v>
@@ -775,7 +842,7 @@
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -790,10 +857,10 @@
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -858,13 +925,13 @@
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="L3" t="n">
         <v>6.4</v>
@@ -873,40 +940,40 @@
         <v>16.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.387</v>
+        <v>0.385</v>
       </c>
       <c r="O3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.78</v>
+        <v>0.773</v>
       </c>
       <c r="R3" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.7</v>
       </c>
       <c r="U3" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X3" t="n">
         <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
         <v>23.1</v>
@@ -915,22 +982,22 @@
         <v>22.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.5</v>
+        <v>101.4</v>
       </c>
       <c r="AC3" t="n">
         <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
         <v>11</v>
@@ -957,19 +1024,19 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
@@ -978,13 +1045,13 @@
         <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX3" t="n">
         <v>15</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1209,7 @@
         <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -1210,46 +1277,46 @@
         <v>52</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>0.423</v>
+        <v>0.442</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J5" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.375</v>
+        <v>0.378</v>
       </c>
       <c r="O5" t="n">
         <v>18.8</v>
       </c>
       <c r="P5" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.785</v>
+        <v>0.782</v>
       </c>
       <c r="R5" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S5" t="n">
         <v>30.3</v>
@@ -1258,7 +1325,7 @@
         <v>42.3</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
         <v>15</v>
@@ -1270,19 +1337,19 @@
         <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
         <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.1</v>
+        <v>100.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
         <v>14</v>
@@ -1291,7 +1358,7 @@
         <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
         <v>21</v>
@@ -1318,34 +1385,34 @@
         <v>9</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP5" t="n">
         <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
@@ -1354,13 +1421,13 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -1389,94 +1456,94 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>0.784</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J6" t="n">
-        <v>78.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.384</v>
+        <v>0.382</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R6" t="n">
         <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.2</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>25</v>
@@ -1485,7 +1552,7 @@
         <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
@@ -1497,19 +1564,19 @@
         <v>4</v>
       </c>
       <c r="AN6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO6" t="n">
         <v>22</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
         <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1518,28 +1585,28 @@
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
       </c>
       <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
         <v>4</v>
       </c>
-      <c r="AY6" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
         <v>21</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -1571,61 +1638,61 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" t="n">
         <v>31</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0.596</v>
+        <v>0.608</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J7" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L7" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M7" t="n">
         <v>19.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O7" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P7" t="n">
         <v>21.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.821</v>
+        <v>0.82</v>
       </c>
       <c r="R7" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S7" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W7" t="n">
         <v>7.3</v>
@@ -1637,31 +1704,31 @@
         <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
@@ -1670,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>13</v>
@@ -1691,16 +1758,16 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
@@ -1718,13 +1785,13 @@
         <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1858,10 +1925,10 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,7 +1940,7 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>-0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF9" t="n">
         <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
         <v>12</v>
@@ -2049,13 +2116,13 @@
         <v>27</v>
       </c>
       <c r="AP9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ9" t="n">
         <v>26</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
         <v>17</v>
@@ -2064,7 +2131,7 @@
         <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>0.352</v>
+        <v>0.34</v>
       </c>
       <c r="H10" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J10" t="n">
-        <v>85.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0.455</v>
@@ -2144,37 +2211,37 @@
         <v>6.6</v>
       </c>
       <c r="M10" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O10" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="P10" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.778</v>
+        <v>0.774</v>
       </c>
       <c r="R10" t="n">
         <v>11.9</v>
       </c>
       <c r="S10" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U10" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="V10" t="n">
         <v>14.8</v>
       </c>
       <c r="W10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X10" t="n">
         <v>6.5</v>
@@ -2183,19 +2250,19 @@
         <v>5.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="AB10" t="n">
         <v>107.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,13 +2274,13 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK10" t="n">
         <v>15</v>
@@ -2222,10 +2289,10 @@
         <v>14</v>
       </c>
       <c r="AM10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2240,10 +2307,10 @@
         <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
       </c>
       <c r="AF11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG11" t="n">
         <v>9</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>8</v>
       </c>
       <c r="AH11" t="n">
         <v>20</v>
@@ -2419,16 +2486,16 @@
         <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2577,10 +2644,10 @@
         <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2604,7 +2671,7 @@
         <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>3</v>
@@ -2625,7 +2692,7 @@
         <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2768,7 +2835,7 @@
         <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN13" t="n">
         <v>25</v>
@@ -2795,7 +2862,7 @@
         <v>15</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
         <v>22</v>
@@ -2807,7 +2874,7 @@
         <v>24</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.804</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="J14" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="K14" t="n">
         <v>0.479</v>
@@ -2872,40 +2939,40 @@
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.366</v>
+        <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="P14" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R14" t="n">
         <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U14" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V14" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W14" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y14" t="n">
         <v>4.5</v>
@@ -2914,16 +2981,16 @@
         <v>20.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.9</v>
+        <v>108.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2935,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2968,7 +3035,7 @@
         <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2977,10 +3044,10 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
@@ -2989,7 +3056,7 @@
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -2998,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>0.538</v>
+        <v>0.529</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3239,34 +3306,34 @@
         <v>19.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O16" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P16" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.741</v>
+        <v>0.739</v>
       </c>
       <c r="R16" t="n">
         <v>10.3</v>
       </c>
       <c r="S16" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T16" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="U16" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V16" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="X16" t="n">
         <v>5.6</v>
@@ -3278,7 +3345,7 @@
         <v>20.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB16" t="n">
         <v>96.3</v>
@@ -3287,10 +3354,10 @@
         <v>0.1</v>
       </c>
       <c r="AD16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="n">
         <v>14</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>13</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
@@ -3299,7 +3366,7 @@
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
         <v>18</v>
@@ -3308,7 +3375,7 @@
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3323,16 +3390,16 @@
         <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>25</v>
@@ -3341,10 +3408,10 @@
         <v>26</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
         <v>6</v>
@@ -3353,10 +3420,10 @@
         <v>6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB16" t="n">
         <v>24</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17" t="n">
         <v>26</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.481</v>
+        <v>0.473</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3409,7 +3476,7 @@
         <v>36.7</v>
       </c>
       <c r="J17" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K17" t="n">
         <v>0.451</v>
@@ -3418,58 +3485,58 @@
         <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O17" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P17" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R17" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X17" t="n">
         <v>3.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3499,7 +3566,7 @@
         <v>22</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
         <v>7</v>
@@ -3508,13 +3575,13 @@
         <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR17" t="n">
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
         <v>15</v>
@@ -3532,10 +3599,10 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3684,7 +3751,7 @@
         <v>28</v>
       </c>
       <c r="AO18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP18" t="n">
         <v>17</v>
@@ -3699,10 +3766,10 @@
         <v>18</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
@@ -3720,7 +3787,7 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3869,13 +3936,13 @@
         <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
         <v>19</v>
@@ -3887,10 +3954,10 @@
         <v>28</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
         <v>21</v>
@@ -3908,7 +3975,7 @@
         <v>19</v>
       </c>
       <c r="BC19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
         <v>11</v>
@@ -4024,7 +4091,7 @@
         <v>8</v>
       </c>
       <c r="AG20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
@@ -4045,10 +4112,10 @@
         <v>10</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
@@ -4069,7 +4136,7 @@
         <v>27</v>
       </c>
       <c r="AV20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
         <v>9</v>
@@ -4078,7 +4145,7 @@
         <v>22</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ20" t="n">
         <v>14</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
         <v>23</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4400,7 +4467,7 @@
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,7 +4476,7 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>8</v>
@@ -4418,16 +4485,16 @@
         <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS22" t="n">
         <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>8.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>20</v>
@@ -4582,7 +4649,7 @@
         <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4636,7 +4703,7 @@
         <v>8</v>
       </c>
       <c r="BC23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -4743,19 +4810,19 @@
         <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF24" t="n">
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
         <v>14</v>
@@ -4800,7 +4867,7 @@
         <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX24" t="n">
         <v>8</v>
@@ -4818,7 +4885,7 @@
         <v>23</v>
       </c>
       <c r="BC24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>0.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4964,7 +5031,7 @@
         <v>4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>27</v>
@@ -4991,7 +5058,7 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -5044,31 +5111,31 @@
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="J26" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="N26" t="n">
         <v>0.383</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P26" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
@@ -5080,10 +5147,10 @@
         <v>41</v>
       </c>
       <c r="U26" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V26" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="W26" t="n">
         <v>6.9</v>
@@ -5092,22 +5159,22 @@
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="AA26" t="n">
         <v>21.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5125,7 +5192,7 @@
         <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="n">
         <v>8</v>
@@ -5137,16 +5204,16 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,28 +5225,28 @@
         <v>17</v>
       </c>
       <c r="AU26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV26" t="n">
         <v>7</v>
       </c>
       <c r="AW26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>29</v>
@@ -5301,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="n">
         <v>22</v>
@@ -5343,7 +5410,7 @@
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW27" t="n">
         <v>24</v>
@@ -5355,13 +5422,13 @@
         <v>20</v>
       </c>
       <c r="AZ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5516,7 +5583,7 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
         <v>22</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -5686,10 +5753,10 @@
         <v>10</v>
       </c>
       <c r="AO29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,13 +5765,13 @@
         <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
         <v>8</v>
@@ -5713,7 +5780,7 @@
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>2.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>11</v>
@@ -5880,7 +5947,7 @@
         <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-8</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6056,7 +6123,7 @@
         <v>28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
         <v>9</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-12-2008-09</t>
+          <t>2009-02-12</t>
         </is>
       </c>
     </row>
